--- a/affiliate_data/เสื้อผ้าแฟชั่นผู้หญิง.xlsx
+++ b/affiliate_data/เสื้อผ้าแฟชั่นผู้หญิง.xlsx
@@ -442,37 +442,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหรา สวมสบายแต่มีสไตล์สําหรับฤดูใบไม้ผลิ/ฤดูร้อนสําหรับผู้หญิง LK4ED1805</v>
+        <v>PRAEWARIN (แพร-วรินทร์) ชุดเดรสผ้าไทยแต่งเข็มกลัดโบว์ ทอลายรวงข้าวแพทเทิร์นสวยหรู</v>
       </c>
       <c r="C2" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823q9-morznv5h67f3a5.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mo48ye9y93ie73.webp</v>
       </c>
       <c r="D2" t="str">
-        <v>314.00</v>
+        <v>1445.00</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="G2" t="str">
-        <v>ขายได้ 142 ชิ้น</v>
+        <v>ขายได้ 13 ชิ้น</v>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>https://shopee.co.th/product/0/49106881566</v>
+        <v>https://shopee.co.th/product/0/55560317121</v>
       </c>
       <c r="J2" t="str">
-        <v>https://s.shopee.co.th/9KfIsKXWbM</v>
+        <v>https://s.shopee.co.th/3B4paYBYEO</v>
       </c>
       <c r="K2" t="str">
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -480,13 +480,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>ชุดเดรสคอกลม แขนสั้น ชุดนอนกระโปรงแขนสั้น ชุดนอนคนแก่ ชุดนอนผู้สูงอายุ ชุดนอนคนสูงอายุ ชุดอยู่บ้าน</v>
+        <v>ชุดเซ็ต2ชิ้น เสื้อ McDonald's สีแดง❤️ + กางเกงขาสั้นแต่งแถบ สวยมากๆ ราคาเซล‼️</v>
       </c>
       <c r="C3" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mmbvlq3rplhc74.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mo75pagionph41.webp</v>
       </c>
       <c r="D3" t="str">
-        <v>85.00</v>
+        <v>149.00</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -495,22 +495,22 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>ขายได้ 625 ชิ้น</v>
+        <v>ขายได้ 89 ชิ้น</v>
       </c>
       <c r="H3" t="str">
         <v/>
       </c>
       <c r="I3" t="str">
-        <v>https://shopee.co.th/product/0/49657343541</v>
+        <v>https://shopee.co.th/product/0/50960084630</v>
       </c>
       <c r="J3" t="str">
-        <v>https://s.shopee.co.th/3B4fX05Ni6</v>
+        <v>https://s.shopee.co.th/2g8YzdMsAc</v>
       </c>
       <c r="K3" t="str">
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -518,37 +518,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Neena Dress มี 2 ไซส์ เดรสปาดไหล่สุดน่ารักเซ็กซี่ซนๆ กระโปรงกางเกงทรงสั้นพริ้วๆ ใครมีปัญหาต้นแขนใหญ่ทรงนี้ช่วยอำพรางได้</v>
+        <v>NEW DROP JINNY PANTS 🤍 กางเกงจินนี่</v>
       </c>
       <c r="C4" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0g-mcs6kvres3fi7c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnsgedf6sirs52.webp</v>
       </c>
       <c r="D4" t="str">
-        <v>436.00</v>
+        <v>466.00</v>
       </c>
       <c r="E4" t="str">
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 246 ชิ้น</v>
       </c>
       <c r="H4" t="str">
         <v/>
       </c>
       <c r="I4" t="str">
-        <v>https://shopee.co.th/product/0/42810806529</v>
+        <v>https://shopee.co.th/product/0/52759875819</v>
       </c>
       <c r="J4" t="str">
-        <v>https://s.shopee.co.th/50WJiN7Xrn</v>
+        <v>https://s.shopee.co.th/2LVib1WBWj</v>
       </c>
       <c r="K4" t="str">
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5">
@@ -556,37 +556,37 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ แต่งลูกไม้ น่ารักมากกกกก</v>
+        <v>mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้หญิง สปอร์ตบราคล้องคอ กางเกงเอวสูงขาบาน ฟิตเนส โยคะ พิลาทิส</v>
       </c>
       <c r="C5" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moja5b8vrcowf4.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mlj23aw571fm70.webp</v>
       </c>
       <c r="D5" t="str">
-        <v>199.00</v>
+        <v>690.00</v>
       </c>
       <c r="E5" t="str">
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>22</v>
       </c>
       <c r="G5" t="str">
-        <v>ขายได้ 103 ชิ้น</v>
+        <v>ขายได้ 87 ชิ้น</v>
       </c>
       <c r="H5" t="str">
         <v/>
       </c>
       <c r="I5" t="str">
-        <v>https://shopee.co.th/product/0/50909890834</v>
+        <v>https://shopee.co.th/product/0/45556927044</v>
       </c>
       <c r="J5" t="str">
-        <v>https://s.shopee.co.th/8V6Bsnygow</v>
+        <v>https://s.shopee.co.th/5AptyETiVY</v>
       </c>
       <c r="K5" t="str">
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -594,37 +594,37 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>น้อมจิตต์ N01 เสื้อเนตรนารี ผู้หญิง ชุดนักเรียน สาขาบางกะปิ</v>
+        <v>🤎Sunny Beach🤎กางเกงขาสั้นผู้หญิง สไตล์เรโทรอเมริกัน ทรงเอวต่ำ ทรงหลวม เหมาะสำหรับทุกโอกาส</v>
       </c>
       <c r="C6" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-mfawbu70mbkd2c.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-8260p-mk21nk3nueire4.webp</v>
       </c>
       <c r="D6" t="str">
-        <v>345.00</v>
+        <v>125.00</v>
       </c>
       <c r="E6" t="str">
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>63</v>
       </c>
       <c r="G6" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 33 ชิ้น</v>
       </c>
       <c r="H6" t="str">
         <v/>
       </c>
       <c r="I6" t="str">
-        <v>https://shopee.co.th/product/0/7918019344</v>
+        <v>https://shopee.co.th/product/0/25447938091</v>
       </c>
       <c r="J6" t="str">
-        <v>https://s.shopee.co.th/3qKMKERnXs</v>
+        <v>https://s.shopee.co.th/60P0xlZgh1</v>
       </c>
       <c r="K6" t="str">
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -632,37 +632,37 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>ถุงเท้านีกเรียนขาวพื้นเทาป้ายกล้วยแพ๊ค12คู่</v>
+        <v>Salu bare pink (เดรสยาวสาลูสีชมพูอ่อน)</v>
       </c>
       <c r="C7" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7quky-lha3mhkghnoo9e.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztm-mjve9fy34gld2b.webp</v>
       </c>
       <c r="D7" t="str">
-        <v>66.00</v>
+        <v>590.00</v>
       </c>
       <c r="E7" t="str">
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>4</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>ขายได้ 965 ชิ้น</v>
+        <v>ขายได้ 50 ชิ้น</v>
       </c>
       <c r="H7" t="str">
         <v/>
       </c>
       <c r="I7" t="str">
-        <v>https://shopee.co.th/product/0/18780262366</v>
+        <v>https://shopee.co.th/product/0/43878304275</v>
       </c>
       <c r="J7" t="str">
-        <v>https://s.shopee.co.th/9pbZTG9Ddg</v>
+        <v>https://s.shopee.co.th/AKY07jRvCf</v>
       </c>
       <c r="K7" t="str">
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -670,31 +670,31 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผลิ/ฤดูร้อนสำหรับผู้หญิง L179AD086</v>
+        <v>Lovito เสื้อหรือกางเกงสไตล์รีสอร์ทดอกไม้หรูหรา สวมสบายแต่มีสไตล์สําหรับฤดูใบไม้ผลิ/ฤดูร้อนสําหรับผู้หญิง LK4ED1805</v>
       </c>
       <c r="C8" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823qh-morzmx2yxfrg97.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823q9-morznv5h67f3a5.webp</v>
       </c>
       <c r="D8" t="str">
-        <v>221.00</v>
+        <v>314.00</v>
       </c>
       <c r="E8" t="str">
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>ขายได้ 3พัน+ ชิ้น</v>
+        <v>ขายได้ 153 ชิ้น</v>
       </c>
       <c r="H8" t="str">
         <v/>
       </c>
       <c r="I8" t="str">
-        <v>https://shopee.co.th/product/0/24697989750</v>
+        <v>https://shopee.co.th/product/0/49106881566</v>
       </c>
       <c r="J8" t="str">
-        <v>https://s.shopee.co.th/9ALsg2LWDc</v>
+        <v>https://s.shopee.co.th/7VDokWlZmU</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -708,37 +708,37 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Sheprem ชุดSet งานปักShePrem ใส่แล้วลุคดูดี โครตสวย โครตปัง ต้องยกให้ชุดนี้เลยค่า ผ้าใส่สบาย ขากระบอกตัดขาไม่เสียทรง</v>
+        <v>ส่งฟรี‼️Bloom Boom บราอกชิด เก็บทรง ซิลิโคนพรีเมียม ( Premium silicone bra)</v>
       </c>
       <c r="C9" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mo6kr9h7zpqe24.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnl3kp620gzp56.webp</v>
       </c>
       <c r="D9" t="str">
-        <v>225.00</v>
+        <v>299.00</v>
       </c>
       <c r="E9" t="str">
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="G9" t="str">
-        <v>ขายได้ 118 ชิ้น</v>
+        <v>ขายได้ 50พัน+ ชิ้น</v>
       </c>
       <c r="H9" t="str">
         <v/>
       </c>
       <c r="I9" t="str">
-        <v>https://shopee.co.th/product/0/52756862606</v>
+        <v>https://shopee.co.th/product/0/18941858027</v>
       </c>
       <c r="J9" t="str">
-        <v>https://s.shopee.co.th/809vHtZip0</v>
+        <v>https://s.shopee.co.th/3VhfzB9XCL</v>
       </c>
       <c r="K9" t="str">
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -746,37 +746,37 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>JINNCHIC เสื้อสายเดี่ยวผู้หญิง แขนกุด ลายทาง แต่งลูกไม้ สไตล์เซ็กซี่หวานๆ เข้ารูป ช่วยพรางหุ่น</v>
+        <v>𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง</v>
       </c>
       <c r="C10" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mji22gcs4jk487.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnjsnsvs035ud9.webp</v>
       </c>
       <c r="D10" t="str">
-        <v>168.00</v>
+        <v>149.00</v>
       </c>
       <c r="E10" t="str">
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>50</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>ขายได้ 566 ชิ้น</v>
+        <v>ขายได้ 317 ชิ้น</v>
       </c>
       <c r="H10" t="str">
         <v/>
       </c>
       <c r="I10" t="str">
-        <v>https://shopee.co.th/product/0/27294039491</v>
+        <v>https://shopee.co.th/product/0/55257246576</v>
       </c>
       <c r="J10" t="str">
-        <v>https://s.shopee.co.th/9zuzfZWZoE</v>
+        <v>https://s.shopee.co.th/4LGmyiFEKo</v>
       </c>
       <c r="K10" t="str">
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -784,37 +784,37 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>B BLUES กางเกงยีนส์ขาสั้นผู้หญิงย้อนยุคสีทึบฤดูร้อนอินเทรนด์กางเกงยีนส์กลางหลวมจัดส่งจากกรุงเทพ</v>
+        <v>Lovito เดรสลําลองผู้หญิงผ้าพลิ้วสไตล์ Ruffle ฤดูร้อน/ฤดูใบไม้ผลิ สีคากี LK4ED853</v>
       </c>
       <c r="C11" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ras9-mb27hlhuj89c81.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823oo-morz7162e7lud1.webp</v>
       </c>
       <c r="D11" t="str">
-        <v>207.00</v>
+        <v>271.00</v>
       </c>
       <c r="E11" t="str">
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G11" t="str">
-        <v>ขายได้ 2พัน+ ชิ้น</v>
+        <v>ขายได้ 7 ชิ้น</v>
       </c>
       <c r="H11" t="str">
         <v/>
       </c>
       <c r="I11" t="str">
-        <v>https://shopee.co.th/product/0/41904664858</v>
+        <v>https://shopee.co.th/product/0/46609023053</v>
       </c>
       <c r="J11" t="str">
-        <v>https://s.shopee.co.th/50WJiNx2HF</v>
+        <v>https://s.shopee.co.th/3B4paZThz8</v>
       </c>
       <c r="K11" t="str">
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -822,37 +822,37 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>ส่งฟรี‼️Bloom Boom บราอกชิด เก็บทรง ซิลิโคนพรีเมียม ( Premium silicone bra)</v>
+        <v>CHUUCHOP - (XS-4XL) Rocky short jeans กางเกงยีนส์ขาสั้นผู้หญิง เอวสูง ผ้ายืด ยีนส์ขาสั้น รับซัมเมอร์ (C9300)</v>
       </c>
       <c r="C12" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztp-mnl3kp620gzp56.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0l-mcf7aqssllcseb.webp</v>
       </c>
       <c r="D12" t="str">
-        <v>309.00</v>
+        <v>554.00</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="G12" t="str">
-        <v>ขายได้ 50พัน+ ชิ้น</v>
+        <v>ขายได้ 5พัน+ ชิ้น</v>
       </c>
       <c r="H12" t="str">
         <v/>
       </c>
       <c r="I12" t="str">
-        <v>https://shopee.co.th/product/0/18941858027</v>
+        <v>https://shopee.co.th/product/0/26430645136</v>
       </c>
       <c r="J12" t="str">
-        <v>https://s.shopee.co.th/1BJb9LLjbF</v>
+        <v>https://s.shopee.co.th/AAEZvR5k0j</v>
       </c>
       <c r="K12" t="str">
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -860,37 +860,37 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Lovito เสื้อเบลาส์หรือกางเกงสุดสง่างาม กระดุมเรียบง่าย ใส่สบายแต่มีสไตล์ สําหรับฤดูใบไม้ผลิ/ฤดูร้อน เสื้อเบลาส์สีอ่อนกากี สําหรับผู้หญิง L178ED1367</v>
+        <v>กางเกงขากว้างผ้าไหมน้ำแข็งสีตัดกันสำหรับผู้หญิงฤดูร้อนบาง 2026 กางเกงขายาวทรงตรงเอวสูงเนื้อหลวมใหม่</v>
       </c>
       <c r="C13" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823qf-morzt9hil1ceb8.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-7rasm-m9ldl588vckgcc.webp</v>
       </c>
       <c r="D13" t="str">
-        <v>140.00</v>
+        <v>129.00</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="G13" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H13" t="str">
         <v/>
       </c>
       <c r="I13" t="str">
-        <v>https://shopee.co.th/product/0/44855875484</v>
+        <v>https://shopee.co.th/product/0/41550419509</v>
       </c>
       <c r="J13" t="str">
-        <v>https://s.shopee.co.th/W3uM7VlXE</v>
+        <v>https://s.shopee.co.th/6py7xJRELB</v>
       </c>
       <c r="K13" t="str">
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -898,13 +898,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Garcon Random buttons Off shoulder | เสื้อปาดไหล่ปักกระดุม</v>
+        <v>Jinni pastel เสื้อสายเดี่ยว กางเกงทรงจินนี่ แต่งลูกไม้ น่ารักมากกกกก</v>
       </c>
       <c r="C14" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zti-mncrk57xd9ttc2.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztq-moja5b8vrcowf4.webp</v>
       </c>
       <c r="D14" t="str">
-        <v>690.00</v>
+        <v>199.00</v>
       </c>
       <c r="E14" t="str">
         <v/>
@@ -913,22 +913,22 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>ขายได้ 193 ชิ้น</v>
+        <v>ขายได้ 182 ชิ้น</v>
       </c>
       <c r="H14" t="str">
         <v/>
       </c>
       <c r="I14" t="str">
-        <v>https://shopee.co.th/product/0/41177947731</v>
+        <v>https://shopee.co.th/product/0/50909890834</v>
       </c>
       <c r="J14" t="str">
-        <v>https://s.shopee.co.th/9ALsg32tgW</v>
+        <v>https://s.shopee.co.th/8pjCKzTn5Y</v>
       </c>
       <c r="K14" t="str">
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -936,31 +936,31 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>🫧Beautified🫧มินิเดรสสีครีม สายเดี่ยว ดีไซน์แต่งขอบและชายผ้าสีแดง กระโปรงทรงเอ ผ้าสเปนเด็กซ์ ไม่ยับ S-XL👗11004</v>
+        <v>Lovito เดรสลำลองผูกโบว์สีชมพูสำหรับฤดูใบไม้ผลิ/ฤดูร้อนสำหรับผู้หญิง L179AD086</v>
       </c>
       <c r="C15" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mm2yrlj32olcb2.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823qh-morzmx2yxfrg97.webp</v>
       </c>
       <c r="D15" t="str">
-        <v>147.00</v>
+        <v>221.00</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="G15" t="str">
-        <v>ขายได้ 47 ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>https://shopee.co.th/product/0/51557483998</v>
+        <v>https://shopee.co.th/product/0/24697989750</v>
       </c>
       <c r="J15" t="str">
-        <v>https://s.shopee.co.th/8fPc58ILMA</v>
+        <v>https://s.shopee.co.th/60P0xmml2e</v>
       </c>
       <c r="K15" t="str">
         <v/>
@@ -974,31 +974,31 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>mofitt.muse|Serene Muse Set ชุดออกกำลังกายผู้หญิง สปอร์ตบราคล้องคอ กางเกงเอวสูงขาบาน ฟิตเนส โยคะ พิลาทิส</v>
+        <v>Ava_SP097 – กางเกงทรงจอร์จ สามส่วน ผ้าคอตตอนยีนส์ ใส่สบาย พรางต้นขา ใส่ได้ทั้งเอวสูงและเอวต่ำ</v>
       </c>
       <c r="C16" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mlj23aw571fm70.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztf-mgq3l3yepamn2a.webp</v>
       </c>
       <c r="D16" t="str">
-        <v>690.00</v>
+        <v>391.00</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G16" t="str">
-        <v>ขายได้ 84 ชิ้น</v>
+        <v>ขายได้ 2พัน+ ชิ้น</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>https://shopee.co.th/product/0/45556927044</v>
+        <v>https://shopee.co.th/product/0/44223244681</v>
       </c>
       <c r="J16" t="str">
-        <v>https://s.shopee.co.th/9KfIsMJrUM</v>
+        <v>https://s.shopee.co.th/6L1rMOpXq6</v>
       </c>
       <c r="K16" t="str">
         <v/>
@@ -1012,37 +1012,37 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Lovito ชุดกางเกงขาสั้นลําลอง เซ็ตฤดูใบไม้ผลิ/ฤดูร้อน กางเกงขาสั้นสีชมพูสําหรับผู้หญิง LK5ED204</v>
+        <v>Choosedress A2032 Penny Mini Cami เสื้อสายเดี่ยว เสื้อสายเดี่ยวลายจุด สกรีนลายหัวใจ</v>
       </c>
       <c r="C17" t="str">
-        <v>https://down-bs-th.img.susercontent.com/sg-11134201-823oy-morzagsuvvnxd0.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztc-mp1twlhthn2jd3.webp</v>
       </c>
       <c r="D17" t="str">
-        <v>272.00</v>
+        <v>250.00</v>
       </c>
       <c r="E17" t="str">
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>30</v>
+        <v/>
       </c>
       <c r="G17" t="str">
-        <v>ขายได้ 76 ชิ้น</v>
+        <v>ขายได้ 243 ชิ้น</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>https://shopee.co.th/product/0/44807681470</v>
+        <v>https://shopee.co.th/product/0/45306268048</v>
       </c>
       <c r="J17" t="str">
-        <v>https://s.shopee.co.th/1VwRXxw8cl</v>
+        <v>https://s.shopee.co.th/9zv9j8kjHA</v>
       </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1050,37 +1050,37 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>BEMYCHICเสื้อสายเดี่ยวปรับสายรุ่นBenny</v>
+        <v>L'NADA ชุดเซ็ทลูกไม้ 2 ชิ้น พร้อมกระโปรงดีเทลคาดเอวลูกไม้ (SetscropNew)</v>
       </c>
       <c r="C18" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zte-mmc6jrnmxqtda7.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-miebjaacynly79.webp</v>
       </c>
       <c r="D18" t="str">
-        <v>550.00</v>
+        <v>330.00</v>
       </c>
       <c r="E18" t="str">
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G18" t="str">
-        <v>ขายได้ 352 ชิ้น</v>
+        <v>ขายได้ 349 ชิ้น</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>https://shopee.co.th/product/0/54057653000</v>
+        <v>https://shopee.co.th/product/0/26213015478</v>
       </c>
       <c r="J18" t="str">
-        <v>https://s.shopee.co.th/8V6Bspf78D</v>
+        <v>https://s.shopee.co.th/3g16BVHINf</v>
       </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -1088,13 +1088,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Mookrinstyle • เดรสถักอกกระโปรงยาว ชุดไปทะเลสวยๆ มี 3 สี ใส่เดินชายหาด Bohemians dress</v>
+        <v>#เดรสผ้าทอลายแต่งทูโทนซิปซ่อนด้านหลัง อัดกาวทั้งชุด</v>
       </c>
       <c r="C19" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7r98q-lwhdyymtgxqna6.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztj-me06n2kwfrbb53.webp</v>
       </c>
       <c r="D19" t="str">
-        <v>195.00</v>
+        <v>1000.00</v>
       </c>
       <c r="E19" t="str">
         <v/>
@@ -1103,22 +1103,22 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>ขายได้ 1พัน+ ชิ้น</v>
+        <v>ขายได้ 103 ชิ้น</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>https://shopee.co.th/product/0/22452707431</v>
+        <v>https://shopee.co.th/product/0/40715794833</v>
       </c>
       <c r="J19" t="str">
-        <v>https://s.shopee.co.th/LkU9pJ8nA</v>
+        <v>https://s.shopee.co.th/9Uyt8E3L0m</v>
       </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -1126,37 +1126,37 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>CHUUCHOP - (XS-4XL) Rocky short jeans กางเกงยีนส์ขาสั้นผู้หญิง เอวสูง ผ้ายืด ยีนส์ขาสั้น รับซัมเมอร์ (C9300)</v>
+        <v>กางเกงขากระบอก กางเกงขายาวผู้หญิง ทรงหลวม ปักน้องหมา แมทช์ง่ายมาก สวยแก๋ #111325</v>
       </c>
       <c r="C20" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-7ra0l-mcf7aqssllcseb.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztk-mhk7v01jq96w91.webp</v>
       </c>
       <c r="D20" t="str">
-        <v>590.00</v>
+        <v>299.00</v>
       </c>
       <c r="E20" t="str">
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="G20" t="str">
-        <v>ขายได้ 5พัน+ ชิ้น</v>
+        <v>ขายได้ 258 ชิ้น</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>https://shopee.co.th/product/0/26430645136</v>
+        <v>https://shopee.co.th/product/0/56352206920</v>
       </c>
       <c r="J20" t="str">
-        <v>https://s.shopee.co.th/9zuzfaluoc</v>
+        <v>https://s.shopee.co.th/2g8YzfZGQa</v>
       </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1164,31 +1164,31 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>𝙎𝙚𝙩 Mสุดแซ่บ❤️ ตามเทรนกันจ้า‼️ได้เสื้อ+กางเกง</v>
+        <v>RUDY-JEWEL LACE CAMI (สีชมพูพร้อมส่ง)ลูกไม้ติดเพชรทั้งตัวสายปรับไม่ได้ความยาวรวมสาย 18‘ไม่ค่อยยืด</v>
       </c>
       <c r="C21" t="str">
-        <v>https://down-bs-th.img.susercontent.com/th-11134207-81zto-mnjsnsvs035ud9.webp</v>
+        <v>https://down-bs-th.img.susercontent.com/th-11134207-81ztn-mkhyv58laq6f7c.webp</v>
       </c>
       <c r="D21" t="str">
-        <v>159.00</v>
+        <v>399.00</v>
       </c>
       <c r="E21" t="str">
         <v/>
       </c>
       <c r="F21" t="str">
-        <v/>
+        <v>27</v>
       </c>
       <c r="G21" t="str">
-        <v>ขายได้ 193 ชิ้น</v>
+        <v>ขายได้ 3พัน+ ชิ้น</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>https://shopee.co.th/product/0/55257246576</v>
+        <v>https://shopee.co.th/product/0/57305992170</v>
       </c>
       <c r="J21" t="str">
-        <v>https://s.shopee.co.th/W3uM8VZHJ</v>
+        <v>https://s.shopee.co.th/1BJlCumsd0</v>
       </c>
       <c r="K21" t="str">
         <v/>
